--- a/output/2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx
+++ b/output/2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx
@@ -495,7 +495,6 @@
           <t>+385 20 222 327 / +385 20 222 328 (mob. +385 99 530 6802)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verificato via WebSearch: sito ufficiale Kärcher + articoli stampa locale (Progressive Magazin, DuList, Dubrovački dnevnik) su apertura sede a Gruž. Vendita/assistenza macchine professionali per pulizia, aspiratori/aspirapolvere industriali Kärcher.</t>
@@ -503,7 +502,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -533,7 +532,6 @@
           <t>020/357096</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Obrt attivo dal 2001, verificato su registri pubblici (fininfo.hr, tvrtke.hr, mojkvart.hr, insolve.hr). Vende e assiste utensili/macchine professionali (Bosch, Metabo, Makita, Dremel, Comet, Wolfcraft, Flex) inclusi aspiratori/prodotti per pulizia industriale.</t>
@@ -541,7 +539,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -583,7 +581,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx
+++ b/output/2026-09-21_00_Croazia_Dubrovačko-neretvanska_Cleaning.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Incluso nonostante sede fuori provincia: distributore/importatore ufficiale Nilfisk per la Croazia dal 2013, con servizio tecnico dichiarato su tutto il territorio nazionale (6 tecnici, copertura Repubblica di Croazia inclusa area Dubrovnik). Verificato via WebSearch sul sito ufficiale crom.hr.</t>
+          <t>Incluso nonostante sede fuori provincia: distributore/importatore ufficiale Nilfisk per la Croazia dal 2013, con servizio tecnico dichiarato su tutto il territorio nazionale (6 tecnici, copertura Repubblica di Croazia inclusa area Dubrovnik). Verificato via WebSearch sul sito ufficiale crom.hr. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
